--- a/pre-week-2/homework2.xlsx
+++ b/pre-week-2/homework2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayaeedarashullahakr\Documents\DataAnalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D34BE00D-9E44-43BD-9126-91C5F3DAEDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{172D2160-3B79-4B11-8EE1-612CCA021BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="4" xr2:uid="{6F22F17B-28EE-41FF-91A5-E2920AB31B6A}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="33" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -179,7 +179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -188,12 +188,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -356,6 +354,62 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -389,6 +443,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-F46D-41C3-A8B1-5945573990A3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -404,6 +463,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-F46D-41C3-A8B1-5945573990A3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -419,6 +483,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-F46D-41C3-A8B1-5945573990A3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -434,6 +503,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-F46D-41C3-A8B1-5945573990A3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2314,7 +2388,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F57A805E-6B44-4920-A137-79F593377BDB}" name="PivotTable7" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F57A805E-6B44-4920-A137-79F593377BDB}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -2356,12 +2430,60 @@
   <dataFields count="1">
     <dataField name="Sum of MonthlySales" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="5">
     <chartFormat chart="1" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -2380,7 +2502,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{07F1FEA8-13F7-48ED-9AE2-9BF314AF68B7}" name="PivotTable10" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{07F1FEA8-13F7-48ED-9AE2-9BF314AF68B7}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -2766,7 +2888,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B3" t="s">
@@ -2774,42 +2896,42 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>593</v>
       </c>
     </row>
@@ -2828,7 +2950,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="82.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2847,7 +2969,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B3" t="s">
@@ -2855,34 +2977,34 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>593</v>
       </c>
     </row>
@@ -2901,7 +3023,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="178.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3104,12 +3226,13 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
+      <c r="A15" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D13">
     <sortCondition descending="1" ref="D2:D13"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>